--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260922.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,978,587</t>
+          <t>603,600</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>603,600</t>
+          <t>1,978,587</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>144,921</t>
+          <t>989,822</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>989,822</t>
+          <t>144,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>571,000</t>
+          <t>434,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>434,000</t>
+          <t>571,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>10,471,121</t>
+          <t>720,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>720,000</t>
+          <t>10,471,121</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,022,578</t>
+          <t>575,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>144,386</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>575,000</t>
+          <t>4,022,578</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>144,386</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>491,000</t>
+          <t>4,899,956</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>4,899,956</t>
+          <t>491,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>168,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>113,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>113,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
